--- a/جدول مواد مصرفی مجتمع 1405.xlsx
+++ b/جدول مواد مصرفی مجتمع 1405.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kerman Computer\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kerman Computer\Desktop\REPORT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CACCBBAC-588B-44F6-9729-8E15B45719BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83AC37DC-269B-42F4-BA26-09A31FDCE60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{048554B0-84FB-4E19-BA5C-2CC4849BC024}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="150">
   <si>
     <t>شرح</t>
   </si>
@@ -435,109 +435,34 @@
     <t>1404/09/26</t>
   </si>
   <si>
-    <t>مصرف  5 ماهه</t>
-  </si>
-  <si>
-    <t>7365 kg</t>
-  </si>
-  <si>
-    <t>137000 kg</t>
-  </si>
-  <si>
-    <t>6000 kg</t>
-  </si>
-  <si>
     <t>57760 kg</t>
   </si>
   <si>
-    <t>2964  kg</t>
-  </si>
-  <si>
-    <t>483000  kg</t>
-  </si>
-  <si>
-    <t>600  kg</t>
-  </si>
-  <si>
     <t>36 m</t>
   </si>
   <si>
-    <t>1084  kg</t>
-  </si>
-  <si>
-    <t>1405 pc</t>
-  </si>
-  <si>
-    <t>2276 pc</t>
-  </si>
-  <si>
-    <t>2833  pc</t>
-  </si>
-  <si>
-    <t>444200  kg</t>
-  </si>
-  <si>
-    <t>1200  pc</t>
-  </si>
-  <si>
-    <t>338  pc</t>
-  </si>
-  <si>
     <t>شاقول چدنی / آهنی</t>
   </si>
   <si>
     <t>54 / 8  pc</t>
   </si>
   <si>
-    <t>6149  kg</t>
-  </si>
-  <si>
     <t>***</t>
   </si>
   <si>
-    <t>262  pc</t>
-  </si>
-  <si>
     <t>177 pc</t>
   </si>
   <si>
-    <t>88  pc</t>
-  </si>
-  <si>
-    <t>89  pc</t>
-  </si>
-  <si>
-    <t>15 pc   /  220  pc</t>
-  </si>
-  <si>
     <t>ول بلوک نازل تاندیش مربع  ( شاموتی/چدنی)</t>
   </si>
   <si>
-    <t>7  pc</t>
-  </si>
-  <si>
-    <t>14920  kg  / 54 pc</t>
-  </si>
-  <si>
     <t>112.5  kg</t>
   </si>
   <si>
     <t>35  kg</t>
   </si>
   <si>
-    <t>1682  pc</t>
-  </si>
-  <si>
-    <t>82  pc</t>
-  </si>
-  <si>
-    <t>11  kg  / 64  pc    25  kg / 6 pc</t>
-  </si>
-  <si>
     <t>per/ton</t>
-  </si>
-  <si>
-    <t>2800 kg</t>
   </si>
   <si>
     <t>نوع جرم نسوز</t>
@@ -606,6 +531,78 @@
   </si>
   <si>
     <t xml:space="preserve">                    جدول مواد مصرفی مجتمع ذوب آهن و فولاد کویر کرمان                                  6 ماهه 1405</t>
+  </si>
+  <si>
+    <t>8170 kg</t>
+  </si>
+  <si>
+    <t>155200 kg</t>
+  </si>
+  <si>
+    <t>18280  kg  / 66 pc</t>
+  </si>
+  <si>
+    <t>7000 kg</t>
+  </si>
+  <si>
+    <t>2559 pc</t>
+  </si>
+  <si>
+    <t>3197  pc</t>
+  </si>
+  <si>
+    <t>520900  kg</t>
+  </si>
+  <si>
+    <t>3044  kg</t>
+  </si>
+  <si>
+    <t>712  kg</t>
+  </si>
+  <si>
+    <t>1372  kg</t>
+  </si>
+  <si>
+    <t>1653 pc</t>
+  </si>
+  <si>
+    <t>1378  pc</t>
+  </si>
+  <si>
+    <t>512  pc</t>
+  </si>
+  <si>
+    <t>3024 kg</t>
+  </si>
+  <si>
+    <t>7019  kg</t>
+  </si>
+  <si>
+    <t>11  kg  / 76  pc    25  kg / 7 pc</t>
+  </si>
+  <si>
+    <t>2146  pc</t>
+  </si>
+  <si>
+    <t>98  pc</t>
+  </si>
+  <si>
+    <t>290  pc</t>
+  </si>
+  <si>
+    <t>102  pc</t>
+  </si>
+  <si>
+    <t>9  pc</t>
+  </si>
+  <si>
+    <t>19 pc   /  302  pc</t>
+  </si>
+  <si>
+    <t>مصرف  6 ماهه</t>
+  </si>
+  <si>
+    <t>547910  kg</t>
   </si>
 </sst>
 </file>
@@ -1307,6 +1304,75 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1334,115 +1400,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1459,6 +1420,42 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1796,26 +1793,26 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:17" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B3" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="54"/>
+      <c r="B3" s="75" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="77"/>
     </row>
     <row r="4" spans="2:17" s="1" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B4" s="55"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="57"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="79"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="80"/>
     </row>
     <row r="5" spans="2:17" s="1" customFormat="1" ht="21.75" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="39" t="s">
@@ -1833,84 +1830,84 @@
       <c r="F5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="71" t="s">
-        <v>106</v>
-      </c>
-      <c r="H5" s="71"/>
+      <c r="G5" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="64"/>
       <c r="I5" s="42" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="72">
+      <c r="B6" s="50">
         <v>1</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="52" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="78" t="s">
+      <c r="E6" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="81"/>
-      <c r="G6" s="65" t="s">
-        <v>107</v>
-      </c>
-      <c r="H6" s="66"/>
-      <c r="I6" s="50"/>
+      <c r="F6" s="56"/>
+      <c r="G6" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" s="59"/>
+      <c r="I6" s="73"/>
     </row>
     <row r="7" spans="2:17" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="73"/>
-      <c r="C7" s="76"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="66"/>
       <c r="D7" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="79"/>
-      <c r="F7" s="82"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="58"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="60"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="81"/>
       <c r="K7" s="43" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="43" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="M7" s="43" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="O7" s="43" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="P7" s="49" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="Q7" s="48"/>
     </row>
     <row r="8" spans="2:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="74"/>
-      <c r="C8" s="77"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="25">
         <v>0.65</v>
       </c>
-      <c r="E8" s="80"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="51"/>
+      <c r="E8" s="55"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="62"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="74"/>
       <c r="K8" s="44">
         <v>1</v>
       </c>
       <c r="L8" s="44" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="M8" s="44" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="N8" s="46">
         <v>0.8</v>
@@ -1918,67 +1915,63 @@
       <c r="O8" s="45">
         <v>3560</v>
       </c>
-      <c r="P8" s="47">
-        <v>0.31900000000000001</v>
-      </c>
+      <c r="P8" s="47"/>
     </row>
     <row r="9" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="72">
+      <c r="B9" s="50">
         <v>2</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="52" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="78" t="s">
+      <c r="E9" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="81"/>
-      <c r="G9" s="65">
+      <c r="F9" s="56"/>
+      <c r="G9" s="58">
         <v>0</v>
       </c>
-      <c r="H9" s="66"/>
-      <c r="I9" s="50"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="73"/>
       <c r="K9" s="44">
         <v>2</v>
       </c>
       <c r="L9" s="44" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="M9" s="44" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="N9" s="46">
         <v>0.81</v>
       </c>
       <c r="O9" s="45">
-        <v>3723</v>
-      </c>
-      <c r="P9" s="47">
-        <v>0.33300000000000002</v>
-      </c>
+        <v>4160</v>
+      </c>
+      <c r="P9" s="47"/>
     </row>
     <row r="10" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="73"/>
-      <c r="C10" s="76"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="66"/>
       <c r="D10" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="79"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="69"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="58"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="60"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="81"/>
       <c r="K10" s="44">
         <v>3</v>
       </c>
       <c r="L10" s="44" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="M10" s="44" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="N10" s="46">
         <v>0.56999999999999995</v>
@@ -1986,29 +1979,27 @@
       <c r="O10" s="45">
         <v>3486</v>
       </c>
-      <c r="P10" s="47">
-        <v>0.312</v>
-      </c>
+      <c r="P10" s="47"/>
     </row>
     <row r="11" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="74"/>
-      <c r="C11" s="77"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="25">
         <v>0.65</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="51"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="74"/>
       <c r="K11" s="44">
         <v>4</v>
       </c>
       <c r="L11" s="44" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="N11" s="46">
         <v>0.68</v>
@@ -2016,67 +2007,63 @@
       <c r="O11" s="45">
         <v>2232</v>
       </c>
-      <c r="P11" s="47">
-        <v>0.2</v>
-      </c>
+      <c r="P11" s="47"/>
     </row>
     <row r="12" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="72">
+      <c r="B12" s="50">
         <v>3</v>
       </c>
-      <c r="C12" s="75" t="s">
+      <c r="C12" s="52" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="81"/>
-      <c r="G12" s="65" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="66"/>
-      <c r="I12" s="50"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="59"/>
+      <c r="I12" s="73"/>
       <c r="K12" s="44">
         <v>5</v>
       </c>
       <c r="L12" s="44" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="N12" s="46">
         <v>0.7</v>
       </c>
       <c r="O12" s="45">
-        <v>6980</v>
-      </c>
-      <c r="P12" s="47">
-        <v>0.625</v>
-      </c>
+        <v>7355</v>
+      </c>
+      <c r="P12" s="47"/>
     </row>
     <row r="13" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="73"/>
-      <c r="C13" s="76"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
       <c r="D13" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="79"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="69"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="58"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="60"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="81"/>
       <c r="K13" s="44">
         <v>6</v>
       </c>
       <c r="L13" s="44" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="M13" s="44" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="N13" s="46">
         <v>0.6</v>
@@ -2084,71 +2071,67 @@
       <c r="O13" s="44">
         <v>880</v>
       </c>
-      <c r="P13" s="47">
-        <v>7.9000000000000001E-2</v>
-      </c>
+      <c r="P13" s="47"/>
     </row>
     <row r="14" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="74"/>
-      <c r="C14" s="77"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="53"/>
       <c r="D14" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="80"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="51"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="63"/>
+      <c r="I14" s="74"/>
       <c r="K14" s="44">
         <v>7</v>
       </c>
       <c r="L14" s="44" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="M14" s="44" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="N14" s="46">
         <v>0.92</v>
       </c>
       <c r="O14" s="44">
-        <v>880</v>
-      </c>
-      <c r="P14" s="47">
-        <v>7.9000000000000001E-2</v>
-      </c>
+        <v>930</v>
+      </c>
+      <c r="P14" s="47"/>
     </row>
     <row r="15" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="72">
+      <c r="B15" s="50">
         <v>4</v>
       </c>
-      <c r="C15" s="75" t="s">
+      <c r="C15" s="52" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="78" t="s">
+      <c r="E15" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="81"/>
-      <c r="G15" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="H15" s="66"/>
-      <c r="I15" s="50"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" s="59"/>
+      <c r="I15" s="73"/>
     </row>
     <row r="16" spans="2:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="74"/>
-      <c r="C16" s="77"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="80"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="51"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="62"/>
+      <c r="H16" s="63"/>
+      <c r="I16" s="74"/>
     </row>
     <row r="17" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B17" s="27">
@@ -2164,10 +2147,10 @@
         <v>65</v>
       </c>
       <c r="F17" s="36"/>
-      <c r="G17" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="H17" s="60"/>
+      <c r="G17" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="70"/>
       <c r="I17" s="38"/>
     </row>
     <row r="18" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2184,45 +2167,45 @@
         <v>66</v>
       </c>
       <c r="F18" s="36"/>
-      <c r="G18" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="H18" s="60"/>
+      <c r="G18" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="70"/>
       <c r="I18" s="38"/>
     </row>
     <row r="19" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="72">
+      <c r="B19" s="50">
         <v>7</v>
       </c>
-      <c r="C19" s="75" t="s">
+      <c r="C19" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="81" t="s">
+      <c r="F19" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="G19" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="H19" s="66"/>
-      <c r="I19" s="50"/>
+      <c r="G19" s="58" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="59"/>
+      <c r="I19" s="73"/>
     </row>
     <row r="20" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="74"/>
-      <c r="C20" s="77"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="80"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="51"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="74"/>
     </row>
     <row r="21" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B21" s="27">
@@ -2238,10 +2221,10 @@
         <v>71</v>
       </c>
       <c r="F21" s="36"/>
-      <c r="G21" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="H21" s="60"/>
+      <c r="G21" s="69" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="70"/>
       <c r="I21" s="38"/>
     </row>
     <row r="22" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2258,75 +2241,75 @@
         <v>72</v>
       </c>
       <c r="F22" s="36"/>
-      <c r="G22" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="60"/>
+      <c r="G22" s="69" t="s">
+        <v>133</v>
+      </c>
+      <c r="H22" s="70"/>
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="72">
+      <c r="B23" s="50">
         <v>10</v>
       </c>
-      <c r="C23" s="75" t="s">
+      <c r="C23" s="52" t="s">
         <v>57</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="81"/>
-      <c r="G23" s="65" t="s">
-        <v>112</v>
-      </c>
-      <c r="H23" s="66"/>
-      <c r="I23" s="50"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="H23" s="59"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="74"/>
-      <c r="C24" s="77"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="53"/>
       <c r="D24" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="80"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="67"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="51"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="74"/>
     </row>
     <row r="25" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="72">
+      <c r="B25" s="50">
         <v>11</v>
       </c>
-      <c r="C25" s="75" t="s">
+      <c r="C25" s="52" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="78" t="s">
+      <c r="E25" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="81"/>
-      <c r="G25" s="65" t="s">
-        <v>113</v>
-      </c>
-      <c r="H25" s="66"/>
-      <c r="I25" s="50"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="58" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="59"/>
+      <c r="I25" s="73"/>
     </row>
     <row r="26" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="74"/>
-      <c r="C26" s="77"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="53"/>
       <c r="D26" s="25">
         <v>0.99</v>
       </c>
-      <c r="E26" s="80"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="51"/>
+      <c r="E26" s="55"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="74"/>
     </row>
     <row r="27" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B27" s="27">
@@ -2342,10 +2325,10 @@
       <c r="F27" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="H27" s="60"/>
+      <c r="G27" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" s="70"/>
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2364,10 +2347,10 @@
       <c r="F28" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="G28" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="H28" s="60"/>
+      <c r="G28" s="69" t="s">
+        <v>135</v>
+      </c>
+      <c r="H28" s="70"/>
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2384,10 +2367,10 @@
         <v>79</v>
       </c>
       <c r="F29" s="36"/>
-      <c r="G29" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="H29" s="60"/>
+      <c r="G29" s="69" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="70"/>
       <c r="I29" s="38"/>
     </row>
     <row r="30" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2404,10 +2387,10 @@
         <v>79</v>
       </c>
       <c r="F30" s="36"/>
-      <c r="G30" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="H30" s="60"/>
+      <c r="G30" s="69" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" s="70"/>
       <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2424,10 +2407,10 @@
         <v>79</v>
       </c>
       <c r="F31" s="36"/>
-      <c r="G31" s="59" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="60"/>
+      <c r="G31" s="69" t="s">
+        <v>138</v>
+      </c>
+      <c r="H31" s="70"/>
       <c r="I31" s="38"/>
     </row>
     <row r="32" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2444,10 +2427,10 @@
         <v>80</v>
       </c>
       <c r="F32" s="36"/>
-      <c r="G32" s="59" t="s">
-        <v>140</v>
-      </c>
-      <c r="H32" s="60"/>
+      <c r="G32" s="69" t="s">
+        <v>139</v>
+      </c>
+      <c r="H32" s="70"/>
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2455,7 +2438,7 @@
         <v>18</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D33" s="29"/>
       <c r="E33" s="29" t="s">
@@ -2464,10 +2447,10 @@
       <c r="F33" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="G33" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="H33" s="60"/>
+      <c r="G33" s="69" t="s">
+        <v>109</v>
+      </c>
+      <c r="H33" s="70"/>
       <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2482,10 +2465,10 @@
         <v>82</v>
       </c>
       <c r="F34" s="36"/>
-      <c r="G34" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="H34" s="60"/>
+      <c r="G34" s="69" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" s="70"/>
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2504,10 +2487,10 @@
       <c r="F35" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="G35" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="H35" s="60"/>
+      <c r="G35" s="69" t="s">
+        <v>110</v>
+      </c>
+      <c r="H35" s="70"/>
       <c r="I35" s="38"/>
     </row>
     <row r="36" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2524,10 +2507,10 @@
       <c r="F36" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="H36" s="60"/>
+      <c r="G36" s="69" t="s">
+        <v>144</v>
+      </c>
+      <c r="H36" s="70"/>
       <c r="I36" s="38"/>
     </row>
     <row r="37" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2546,10 +2529,10 @@
       <c r="F37" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="H37" s="60"/>
+      <c r="G37" s="69" t="s">
+        <v>111</v>
+      </c>
+      <c r="H37" s="70"/>
       <c r="I37" s="38"/>
     </row>
     <row r="38" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2568,10 +2551,10 @@
       <c r="F38" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="G38" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="H38" s="60"/>
+      <c r="G38" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="H38" s="70"/>
       <c r="I38" s="38"/>
     </row>
     <row r="39" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2590,10 +2573,10 @@
       <c r="F39" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="G39" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="H39" s="60"/>
+      <c r="G39" s="69" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" s="70"/>
       <c r="I39" s="38"/>
     </row>
     <row r="40" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2612,10 +2595,10 @@
       <c r="F40" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="G40" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="H40" s="60"/>
+      <c r="G40" s="69" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="70"/>
       <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -2623,7 +2606,7 @@
         <v>26</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>42</v>
@@ -2634,10 +2617,10 @@
       <c r="F41" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="G41" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="H41" s="60"/>
+      <c r="G41" s="69" t="s">
+        <v>147</v>
+      </c>
+      <c r="H41" s="70"/>
       <c r="I41" s="38"/>
     </row>
     <row r="42" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2656,45 +2639,45 @@
       <c r="F42" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="G42" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="H42" s="64"/>
+      <c r="G42" s="82" t="s">
+        <v>128</v>
+      </c>
+      <c r="H42" s="83"/>
       <c r="I42" s="38"/>
     </row>
     <row r="43" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B43" s="72">
+      <c r="B43" s="50">
         <v>28</v>
       </c>
-      <c r="C43" s="75" t="s">
+      <c r="C43" s="52" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="78" t="s">
+      <c r="E43" s="54" t="s">
         <v>92</v>
       </c>
-      <c r="F43" s="81" t="s">
+      <c r="F43" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="G43" s="65" t="s">
+      <c r="G43" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="H43" s="66"/>
-      <c r="I43" s="50"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="73"/>
     </row>
     <row r="44" spans="2:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="74"/>
-      <c r="C44" s="77"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="53"/>
       <c r="D44" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="E44" s="80"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="67"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="51"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="62"/>
+      <c r="H44" s="63"/>
+      <c r="I44" s="74"/>
     </row>
     <row r="45" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
       <c r="B45" s="27">
@@ -2710,10 +2693,10 @@
         <v>104</v>
       </c>
       <c r="F45" s="36"/>
-      <c r="G45" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="H45" s="60"/>
+      <c r="G45" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="H45" s="70"/>
       <c r="I45" s="38"/>
     </row>
     <row r="46" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2730,10 +2713,10 @@
         <v>104</v>
       </c>
       <c r="F46" s="36"/>
-      <c r="G46" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="H46" s="60"/>
+      <c r="G46" s="69" t="s">
+        <v>114</v>
+      </c>
+      <c r="H46" s="70"/>
       <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2748,10 +2731,10 @@
         <v>101</v>
       </c>
       <c r="F47" s="36"/>
-      <c r="G47" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="H47" s="60"/>
+      <c r="G47" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="H47" s="70"/>
       <c r="I47" s="38"/>
     </row>
     <row r="48" spans="2:9" ht="20.25" x14ac:dyDescent="0.25">
@@ -2768,10 +2751,10 @@
         <v>102</v>
       </c>
       <c r="F48" s="36"/>
-      <c r="G48" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="H48" s="60"/>
+      <c r="G48" s="69" t="s">
+        <v>143</v>
+      </c>
+      <c r="H48" s="70"/>
       <c r="I48" s="38"/>
     </row>
     <row r="49" spans="2:9" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2786,35 +2769,54 @@
         <v>103</v>
       </c>
       <c r="F49" s="37"/>
-      <c r="G49" s="61" t="s">
-        <v>138</v>
-      </c>
-      <c r="H49" s="62"/>
+      <c r="G49" s="71" t="s">
+        <v>141</v>
+      </c>
+      <c r="H49" s="72"/>
       <c r="I49" s="38"/>
     </row>
     <row r="50" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="75">
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="E43:E44"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="I43:I44"/>
+    <mergeCell ref="B3:I4"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="G43:H44"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="G25:H26"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G15:H16"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H20"/>
+    <mergeCell ref="G21:H21"/>
     <mergeCell ref="G6:H8"/>
     <mergeCell ref="G9:H11"/>
     <mergeCell ref="G12:H14"/>
@@ -2831,45 +2833,26 @@
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="F12:F14"/>
-    <mergeCell ref="G15:H16"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H20"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G23:H24"/>
-    <mergeCell ref="G25:H26"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="I43:I44"/>
-    <mergeCell ref="B3:I4"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="I12:I14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="G39:H39"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="G43:H44"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="E43:E44"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.3" footer="0.3"/>
@@ -2894,20 +2877,20 @@
   <sheetData>
     <row r="2" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="3" spans="2:6" s="1" customFormat="1" ht="21.75" x14ac:dyDescent="0.5">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="97"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="97"/>
-      <c r="F3" s="98"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="86"/>
     </row>
     <row r="4" spans="2:6" s="1" customFormat="1" ht="22.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
       <c r="E4" s="3" t="s">
         <v>46</v>
       </c>
@@ -2933,126 +2916,126 @@
       </c>
     </row>
     <row r="6" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="84">
+      <c r="B6" s="98">
         <v>1</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="95" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="88" t="s">
+      <c r="E6" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F6" s="90"/>
+      <c r="F6" s="89"/>
     </row>
     <row r="7" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="92"/>
-      <c r="C7" s="95"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="96"/>
       <c r="D7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="94"/>
-      <c r="F7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="90"/>
     </row>
     <row r="8" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="85"/>
-      <c r="C8" s="87"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="10">
         <v>0.65</v>
       </c>
-      <c r="E8" s="89"/>
+      <c r="E8" s="94"/>
       <c r="F8" s="91"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="84">
+      <c r="B9" s="98">
         <v>2</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="95" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="88" t="s">
+      <c r="E9" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="F9" s="90"/>
+      <c r="F9" s="89"/>
     </row>
     <row r="10" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="92"/>
-      <c r="C10" s="95"/>
+      <c r="B10" s="99"/>
+      <c r="C10" s="96"/>
       <c r="D10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="94"/>
-      <c r="F10" s="93"/>
+      <c r="E10" s="93"/>
+      <c r="F10" s="90"/>
     </row>
     <row r="11" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="85"/>
-      <c r="C11" s="87"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="10">
         <v>0.65</v>
       </c>
-      <c r="E11" s="89"/>
+      <c r="E11" s="94"/>
       <c r="F11" s="91"/>
     </row>
     <row r="12" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="84">
+      <c r="B12" s="98">
         <v>3</v>
       </c>
-      <c r="C12" s="86" t="s">
+      <c r="C12" s="95" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="88" t="s">
+      <c r="E12" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="F12" s="90"/>
+      <c r="F12" s="89"/>
     </row>
     <row r="13" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="92"/>
-      <c r="C13" s="95"/>
+      <c r="B13" s="99"/>
+      <c r="C13" s="96"/>
       <c r="D13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="94"/>
-      <c r="F13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="90"/>
     </row>
     <row r="14" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="85"/>
-      <c r="C14" s="87"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="97"/>
       <c r="D14" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="89"/>
+      <c r="E14" s="94"/>
       <c r="F14" s="91"/>
     </row>
     <row r="15" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="84">
+      <c r="B15" s="98">
         <v>4</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="95" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="88" t="s">
+      <c r="E15" s="92" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="90"/>
+      <c r="F15" s="89"/>
     </row>
     <row r="16" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="85"/>
-      <c r="C16" s="87"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="89"/>
+      <c r="E16" s="94"/>
       <c r="F16" s="91"/>
     </row>
     <row r="17" spans="2:6" ht="20.25" x14ac:dyDescent="0.25">
@@ -3086,29 +3069,29 @@
       <c r="F18" s="15"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="84">
+      <c r="B19" s="98">
         <v>7</v>
       </c>
-      <c r="C19" s="86" t="s">
+      <c r="C19" s="95" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="88" t="s">
+      <c r="E19" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="90" t="s">
+      <c r="F19" s="89" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="85"/>
-      <c r="C20" s="87"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="97"/>
       <c r="D20" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E20" s="89"/>
+      <c r="E20" s="94"/>
       <c r="F20" s="91"/>
     </row>
     <row r="21" spans="2:6" ht="20.25" x14ac:dyDescent="0.25">
@@ -3142,51 +3125,51 @@
       <c r="F22" s="15"/>
     </row>
     <row r="23" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="84">
+      <c r="B23" s="98">
         <v>10</v>
       </c>
-      <c r="C23" s="86" t="s">
+      <c r="C23" s="95" t="s">
         <v>57</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="88" t="s">
+      <c r="E23" s="92" t="s">
         <v>73</v>
       </c>
-      <c r="F23" s="90"/>
+      <c r="F23" s="89"/>
     </row>
     <row r="24" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="85"/>
-      <c r="C24" s="87"/>
+      <c r="B24" s="100"/>
+      <c r="C24" s="97"/>
       <c r="D24" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="89"/>
+      <c r="E24" s="94"/>
       <c r="F24" s="91"/>
     </row>
     <row r="25" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="84">
+      <c r="B25" s="98">
         <v>11</v>
       </c>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="95" t="s">
         <v>12</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E25" s="88" t="s">
+      <c r="E25" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="F25" s="90"/>
+      <c r="F25" s="89"/>
     </row>
     <row r="26" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="85"/>
-      <c r="C26" s="87"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="97"/>
       <c r="D26" s="10">
         <v>0.99</v>
       </c>
-      <c r="E26" s="89"/>
+      <c r="E26" s="94"/>
       <c r="F26" s="91"/>
     </row>
     <row r="27" spans="2:6" ht="20.25" x14ac:dyDescent="0.25">
@@ -3444,29 +3427,29 @@
       </c>
     </row>
     <row r="43" spans="2:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B43" s="84">
+      <c r="B43" s="98">
         <v>28</v>
       </c>
-      <c r="C43" s="86" t="s">
+      <c r="C43" s="95" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E43" s="88" t="s">
+      <c r="E43" s="92" t="s">
         <v>92</v>
       </c>
-      <c r="F43" s="90" t="s">
+      <c r="F43" s="89" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="44" spans="2:6" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="85"/>
-      <c r="C44" s="87"/>
+      <c r="B44" s="100"/>
+      <c r="C44" s="97"/>
       <c r="D44" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E44" s="89"/>
+      <c r="E44" s="94"/>
       <c r="F44" s="91"/>
     </row>
     <row r="45" spans="2:6" ht="20.25" x14ac:dyDescent="0.25">
@@ -3541,24 +3524,6 @@
     <row r="50" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="C9:C11"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="F12:F14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C15:C16"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C43:C44"/>
     <mergeCell ref="E43:E44"/>
@@ -3575,6 +3540,24 @@
     <mergeCell ref="C19:C20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="F9:F11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="C9:C11"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="C6:C8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
